--- a/output/pdf_financials_xlsx/ENS.xlsx
+++ b/output/pdf_financials_xlsx/ENS.xlsx
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2002.679</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>18.990615</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>9.739927</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>16.491979</v>
       </c>
     </row>
     <row r="35">
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2002.679</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>18.990615</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>9.739927</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>16.491979</v>
       </c>
     </row>
     <row r="37">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/ENS.xlsx
+++ b/output/pdf_financials_xlsx/ENS.xlsx
@@ -2784,16 +2784,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>23900.38</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.38264</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>7.114551</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>12.973874</v>
       </c>
     </row>
     <row r="116">
@@ -4254,7 +4254,11 @@
           <t>Proceeds from Sale of Investments</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>23900.38</v>
       </c>
@@ -6798,7 +6802,11 @@
           <t>Net Investment Profit (Loss) before Distributions on Preferred Shares</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -6832,7 +6840,11 @@
           <t>Distributions on Preferred Shares (Note 13)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -7476,7 +7488,11 @@
           <t>Net Investment Profit before Distributions on Preferred Shares</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -7510,7 +7526,11 @@
           <t>Distributions on Preferred Shares (Note 14)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -8306,7 +8326,11 @@
           <t>Net Investment Loss before Distributions on Preferred Shares</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="n">
         <v>-3499.884</v>
       </c>
@@ -8342,7 +8366,11 @@
           <t>Distributions on Preferred Shares (Note 11)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E147" s="5" t="n">
         <v>848.688</v>
       </c>
